--- a/docs/pdf/CEF_Detailed_Budget_Table.xlsx
+++ b/docs/pdf/CEF_Detailed_Budget_Table.xlsx
@@ -571,7 +571,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Project Acronym: AETERNA-SCW  // Proposal ID: CEF-DIG-2026-SMART-CABLES-101538202</t>
+          <t>Project Acronym: AETERNA-SCW  // Proposal ID: CEF-DIG-2026-SMART-CABLES-101354145</t>
         </is>
       </c>
     </row>
